--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.54154746757544</v>
+        <v>10.65050146348101</v>
       </c>
       <c r="D2" t="n">
-        <v>61.21478579559027</v>
+        <v>9.947402691783418</v>
       </c>
       <c r="E2" t="n">
-        <v>19.02449752235222</v>
+        <v>3.091480847382236</v>
       </c>
       <c r="F2" t="n">
-        <v>18.17357543999244</v>
+        <v>2.953206008998772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.28582211848137</v>
+        <v>4.271446094253223</v>
       </c>
       <c r="D3" t="n">
-        <v>24.82438317461282</v>
+        <v>4.033962265874584</v>
       </c>
       <c r="E3" t="n">
-        <v>19.02449752235222</v>
+        <v>3.091480847382236</v>
       </c>
       <c r="F3" t="n">
-        <v>18.17357543999244</v>
+        <v>2.953206008998772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.16666666666667</v>
+        <v>3.927083333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>20.81465829649865</v>
+        <v>3.382381973181031</v>
       </c>
       <c r="E4" t="n">
-        <v>19.02449752235222</v>
+        <v>3.091480847382236</v>
       </c>
       <c r="F4" t="n">
-        <v>18.17357543999244</v>
+        <v>2.953206008998772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
